--- a/ig/main/CodeSystem-TRE-A06-FormatCodeComplementaire.xlsx
+++ b/ig/main/CodeSystem-TRE-A06-FormatCodeComplementaire.xlsx
@@ -31,7 +31,7 @@
     <t>Identifier</t>
   </si>
   <si>
-    <t>urn:ietf:rfc:3986#Uniform Resource Identifier (URI)#urn:oid:1.2.250.1.213.1.1.4.2.282</t>
+    <t>OID:1.2.250.1.213.1.1.4.2.282</t>
   </si>
   <si>
     <t>Version</t>

--- a/ig/main/CodeSystem-TRE-A06-FormatCodeComplementaire.xlsx
+++ b/ig/main/CodeSystem-TRE-A06-FormatCodeComplementaire.xlsx
@@ -76,7 +76,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>ANS (https://esante.gouv.fr)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/ig/main/CodeSystem-TRE-A06-FormatCodeComplementaire.xlsx
+++ b/ig/main/CodeSystem-TRE-A06-FormatCodeComplementaire.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="162">
   <si>
     <t>Property</t>
   </si>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-15T12:00:00+01:00</t>
+    <t>2024-03-29T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -900,7 +900,9 @@
       <c r="C2" t="s" s="2">
         <v>51</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>51</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
@@ -1296,7 +1298,9 @@
       <c r="C35" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="D35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>115</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">

--- a/ig/main/CodeSystem-TRE-A06-FormatCodeComplementaire.xlsx
+++ b/ig/main/CodeSystem-TRE-A06-FormatCodeComplementaire.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="167">
   <si>
     <t>Property</t>
   </si>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T12:00:00+01:00</t>
+    <t>2024-04-26T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -500,6 +500,21 @@
   </si>
   <si>
     <t>Feuille de style</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:dlu:2024</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:ft-su:2024</t>
+  </si>
+  <si>
+    <t>Fiche de transfert vers le service des urgences</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:fr-su:2024</t>
+  </si>
+  <si>
+    <t>Fiche de retour du service des urgences</t>
   </si>
 </sst>
 </file>
@@ -873,7 +888,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1602,6 +1617,42 @@
       </c>
       <c r="D60" s="2"/>
     </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="C61" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="D61" s="2"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="C62" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="D62" s="2"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="C63" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="D63" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/ig/main/CodeSystem-TRE-A06-FormatCodeComplementaire.xlsx
+++ b/ig/main/CodeSystem-TRE-A06-FormatCodeComplementaire.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>20240426120000</t>
   </si>
   <si>
     <t>Name</t>

--- a/ig/main/CodeSystem-TRE-A06-FormatCodeComplementaire.xlsx
+++ b/ig/main/CodeSystem-TRE-A06-FormatCodeComplementaire.xlsx
@@ -82,7 +82,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>

--- a/ig/main/CodeSystem-TRE-A06-FormatCodeComplementaire.xlsx
+++ b/ig/main/CodeSystem-TRE-A06-FormatCodeComplementaire.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="169">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20240426120000</t>
+    <t>20240726120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-26T12:00:00+01:00</t>
+    <t>2024-07-26T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -515,6 +515,12 @@
   </si>
   <si>
     <t>Fiche de retour du service des urgences</t>
+  </si>
+  <si>
+    <t>urn:ans:ci-sis:trod:2024</t>
+  </si>
+  <si>
+    <t>Test rapide d'orientation diagnostique</t>
   </si>
 </sst>
 </file>
@@ -888,7 +894,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D63"/>
+  <dimension ref="A1:D64"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1653,6 +1659,18 @@
       </c>
       <c r="D63" s="2"/>
     </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="C64" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="D64" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
